--- a/docs/Mapping_casi_uso/morte/Morte_006.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_006.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="211">
   <si>
     <t>Sezione</t>
   </si>
@@ -138,6 +138,12 @@
   </si>
   <si>
     <t>testoDataPresuntaMorte</t>
+  </si>
+  <si>
+    <t>Data rinvenimento cadavere</t>
+  </si>
+  <si>
+    <t>dataRinvenimentoCadavere</t>
   </si>
   <si>
     <t>Luogo</t>
@@ -697,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H167"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.12890625" customWidth="true" bestFit="true"/>
@@ -1108,7 +1114,7 @@
         <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>30</v>
@@ -1154,7 +1160,7 @@
         <v>48</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>30</v>
@@ -1286,22 +1292,22 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>21</v>
@@ -1309,22 +1315,22 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>65</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>21</v>
@@ -1332,16 +1338,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>67</v>
@@ -1355,16 +1361,16 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>69</v>
@@ -1378,16 +1384,16 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>71</v>
@@ -1401,7 +1407,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>72</v>
@@ -1410,13 +1416,13 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>21</v>
@@ -1424,22 +1430,22 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>21</v>
@@ -1447,7 +1453,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>76</v>
@@ -1456,7 +1462,7 @@
         <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>77</v>
@@ -1470,7 +1476,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>78</v>
@@ -1479,7 +1485,7 @@
         <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>79</v>
@@ -1493,16 +1499,16 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>81</v>
@@ -1516,7 +1522,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>82</v>
@@ -1525,13 +1531,13 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>21</v>
@@ -1539,7 +1545,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>84</v>
@@ -1548,13 +1554,13 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>21</v>
@@ -1562,7 +1568,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>86</v>
@@ -1571,13 +1577,13 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>87</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>21</v>
@@ -1585,19 +1591,19 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>15</v>
@@ -1608,22 +1614,22 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>90</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>21</v>
@@ -1631,7 +1637,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>91</v>
@@ -1640,7 +1646,7 @@
         <v>12</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>92</v>
@@ -1654,22 +1660,22 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>94</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>21</v>
@@ -1677,7 +1683,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>95</v>
@@ -1686,7 +1692,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>96</v>
@@ -1700,7 +1706,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>97</v>
@@ -1709,13 +1715,13 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>21</v>
@@ -1723,7 +1729,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>99</v>
@@ -1732,13 +1738,13 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>21</v>
@@ -1746,7 +1752,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>101</v>
@@ -1755,13 +1761,13 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>102</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>21</v>
@@ -1769,7 +1775,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>103</v>
@@ -1778,13 +1784,13 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>104</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>21</v>
@@ -1792,7 +1798,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>105</v>
@@ -1801,13 +1807,13 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>106</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>21</v>
@@ -1815,7 +1821,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>107</v>
@@ -1824,13 +1830,13 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>108</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>21</v>
@@ -1838,7 +1844,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>109</v>
@@ -1847,7 +1853,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>110</v>
@@ -1861,22 +1867,22 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>112</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>21</v>
@@ -1884,7 +1890,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>113</v>
@@ -1893,7 +1899,7 @@
         <v>12</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>114</v>
@@ -1907,7 +1913,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>115</v>
@@ -1916,7 +1922,7 @@
         <v>12</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>116</v>
@@ -1930,19 +1936,19 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="C54" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
@@ -1953,16 +1959,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>65</v>
@@ -1976,19 +1982,19 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>10</v>
@@ -1999,19 +2005,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
@@ -2022,16 +2028,16 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>69</v>
@@ -2045,16 +2051,16 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>71</v>
@@ -2068,7 +2074,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>72</v>
@@ -2077,7 +2083,7 @@
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>73</v>
@@ -2091,16 +2097,16 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>75</v>
@@ -2114,16 +2120,16 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>77</v>
@@ -2137,16 +2143,16 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>79</v>
@@ -2160,16 +2166,16 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>81</v>
@@ -2183,16 +2189,16 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>83</v>
@@ -2206,16 +2212,16 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>85</v>
@@ -2229,16 +2235,16 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>87</v>
@@ -2252,19 +2258,19 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -2275,16 +2281,16 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>90</v>
@@ -2298,7 +2304,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>91</v>
@@ -2307,7 +2313,7 @@
         <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>92</v>
@@ -2321,19 +2327,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
@@ -2344,16 +2350,16 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>98</v>
@@ -2367,16 +2373,16 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>100</v>
@@ -2390,16 +2396,16 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>102</v>
@@ -2413,16 +2419,16 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>104</v>
@@ -2436,16 +2442,16 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>106</v>
@@ -2459,16 +2465,16 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>108</v>
@@ -2482,16 +2488,16 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>110</v>
@@ -2505,19 +2511,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2528,7 +2534,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>136</v>
@@ -2537,7 +2543,7 @@
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>137</v>
@@ -2551,7 +2557,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>138</v>
@@ -2560,7 +2566,7 @@
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>139</v>
@@ -2574,7 +2580,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>140</v>
@@ -2583,7 +2589,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>141</v>
@@ -2597,19 +2603,19 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="C83" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
@@ -2620,16 +2626,16 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>147</v>
@@ -2643,7 +2649,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>148</v>
@@ -2652,7 +2658,7 @@
         <v>12</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>149</v>
@@ -2666,19 +2672,19 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
@@ -2689,19 +2695,19 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>151</v>
+        <v>59</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
@@ -2712,16 +2718,16 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>153</v>
@@ -2735,16 +2741,16 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>155</v>
@@ -2758,39 +2764,39 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="C90" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D90" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>158</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>65</v>
@@ -2799,12 +2805,12 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>66</v>
@@ -2813,7 +2819,7 @@
         <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>67</v>
@@ -2822,12 +2828,12 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>68</v>
@@ -2836,7 +2842,7 @@
         <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>69</v>
@@ -2845,12 +2851,12 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>70</v>
@@ -2859,7 +2865,7 @@
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>71</v>
@@ -2868,12 +2874,12 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>72</v>
@@ -2882,7 +2888,7 @@
         <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>73</v>
@@ -2891,12 +2897,12 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>74</v>
@@ -2905,7 +2911,7 @@
         <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>75</v>
@@ -2914,12 +2920,12 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>76</v>
@@ -2928,7 +2934,7 @@
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>77</v>
@@ -2937,12 +2943,12 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>78</v>
@@ -2951,7 +2957,7 @@
         <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>79</v>
@@ -2960,12 +2966,12 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>80</v>
@@ -2974,7 +2980,7 @@
         <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>81</v>
@@ -2983,12 +2989,12 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>82</v>
@@ -2997,7 +3003,7 @@
         <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>83</v>
@@ -3006,12 +3012,12 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>84</v>
@@ -3020,7 +3026,7 @@
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>85</v>
@@ -3029,12 +3035,12 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>86</v>
@@ -3043,7 +3049,7 @@
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>87</v>
@@ -3052,44 +3058,44 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>90</v>
@@ -3098,12 +3104,12 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>91</v>
@@ -3112,7 +3118,7 @@
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>92</v>
@@ -3121,12 +3127,12 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>93</v>
@@ -3135,7 +3141,7 @@
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>94</v>
@@ -3144,12 +3150,12 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>95</v>
@@ -3158,7 +3164,7 @@
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>96</v>
@@ -3167,12 +3173,12 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>97</v>
@@ -3181,7 +3187,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>98</v>
@@ -3190,12 +3196,12 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>99</v>
@@ -3204,7 +3210,7 @@
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>100</v>
@@ -3213,12 +3219,12 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>101</v>
@@ -3227,7 +3233,7 @@
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>102</v>
@@ -3236,12 +3242,12 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>103</v>
@@ -3250,7 +3256,7 @@
         <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>104</v>
@@ -3259,12 +3265,12 @@
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>105</v>
@@ -3273,7 +3279,7 @@
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>106</v>
@@ -3282,12 +3288,12 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>107</v>
@@ -3296,7 +3302,7 @@
         <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>108</v>
@@ -3305,12 +3311,12 @@
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>109</v>
@@ -3319,7 +3325,7 @@
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>110</v>
@@ -3328,12 +3334,12 @@
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>111</v>
@@ -3342,7 +3348,7 @@
         <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>112</v>
@@ -3351,12 +3357,12 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>113</v>
@@ -3365,7 +3371,7 @@
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>114</v>
@@ -3374,12 +3380,12 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>115</v>
@@ -3388,7 +3394,7 @@
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>116</v>
@@ -3397,24 +3403,24 @@
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
@@ -3425,16 +3431,16 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>65</v>
@@ -3443,12 +3449,12 @@
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>66</v>
@@ -3457,7 +3463,7 @@
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>67</v>
@@ -3466,12 +3472,12 @@
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>68</v>
@@ -3480,7 +3486,7 @@
         <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>69</v>
@@ -3489,12 +3495,12 @@
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>70</v>
@@ -3503,7 +3509,7 @@
         <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>71</v>
@@ -3512,12 +3518,12 @@
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>72</v>
@@ -3526,7 +3532,7 @@
         <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>73</v>
@@ -3535,12 +3541,12 @@
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>74</v>
@@ -3549,7 +3555,7 @@
         <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>75</v>
@@ -3558,12 +3564,12 @@
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>76</v>
@@ -3572,7 +3578,7 @@
         <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>77</v>
@@ -3581,12 +3587,12 @@
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>78</v>
@@ -3595,7 +3601,7 @@
         <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>79</v>
@@ -3604,12 +3610,12 @@
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>80</v>
@@ -3618,7 +3624,7 @@
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>81</v>
@@ -3627,12 +3633,12 @@
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>82</v>
@@ -3641,7 +3647,7 @@
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>83</v>
@@ -3650,12 +3656,12 @@
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>84</v>
@@ -3664,7 +3670,7 @@
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>85</v>
@@ -3673,12 +3679,12 @@
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>86</v>
@@ -3687,7 +3693,7 @@
         <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>87</v>
@@ -3696,44 +3702,44 @@
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>90</v>
@@ -3742,12 +3748,12 @@
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>91</v>
@@ -3756,7 +3762,7 @@
         <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>92</v>
@@ -3765,12 +3771,12 @@
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>93</v>
@@ -3779,7 +3785,7 @@
         <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>94</v>
@@ -3788,12 +3794,12 @@
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>95</v>
@@ -3802,7 +3808,7 @@
         <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>96</v>
@@ -3811,12 +3817,12 @@
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>97</v>
@@ -3825,7 +3831,7 @@
         <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>98</v>
@@ -3834,12 +3840,12 @@
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>99</v>
@@ -3848,7 +3854,7 @@
         <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>100</v>
@@ -3857,12 +3863,12 @@
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>101</v>
@@ -3871,7 +3877,7 @@
         <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>102</v>
@@ -3880,12 +3886,12 @@
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>103</v>
@@ -3894,7 +3900,7 @@
         <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>104</v>
@@ -3903,12 +3909,12 @@
         <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>105</v>
@@ -3917,7 +3923,7 @@
         <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>106</v>
@@ -3926,12 +3932,12 @@
         <v>10</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>107</v>
@@ -3940,7 +3946,7 @@
         <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>108</v>
@@ -3949,12 +3955,12 @@
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>109</v>
@@ -3963,7 +3969,7 @@
         <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>110</v>
@@ -3972,12 +3978,12 @@
         <v>10</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>111</v>
@@ -3986,7 +3992,7 @@
         <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>112</v>
@@ -3995,12 +4001,12 @@
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>113</v>
@@ -4009,7 +4015,7 @@
         <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>114</v>
@@ -4018,12 +4024,12 @@
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>115</v>
@@ -4032,7 +4038,7 @@
         <v>9</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>116</v>
@@ -4041,7 +4047,7 @@
         <v>10</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="146">
@@ -4049,36 +4055,36 @@
         <v>161</v>
       </c>
       <c r="B146" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G146" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G146" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>166</v>
@@ -4092,7 +4098,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>167</v>
@@ -4101,7 +4107,7 @@
         <v>12</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>168</v>
@@ -4115,19 +4121,19 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>10</v>
@@ -4138,7 +4144,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>172</v>
@@ -4147,7 +4153,7 @@
         <v>12</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>173</v>
@@ -4161,53 +4167,53 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="C151" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E151" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C151" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="F151" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>178</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E152" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E152" s="2" t="s">
+      <c r="F152" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G152" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>181</v>
@@ -4216,7 +4222,7 @@
         <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>182</v>
@@ -4225,12 +4231,12 @@
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>183</v>
@@ -4239,7 +4245,7 @@
         <v>9</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>184</v>
@@ -4248,12 +4254,12 @@
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>185</v>
@@ -4262,7 +4268,7 @@
         <v>9</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>186</v>
@@ -4271,12 +4277,12 @@
         <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>187</v>
@@ -4285,7 +4291,7 @@
         <v>9</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>188</v>
@@ -4294,12 +4300,12 @@
         <v>10</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>189</v>
@@ -4308,44 +4314,44 @@
         <v>9</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>192</v>
@@ -4354,44 +4360,44 @@
         <v>9</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>194</v>
+        <v>23</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>195</v>
@@ -4400,7 +4406,7 @@
         <v>9</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>196</v>
@@ -4409,12 +4415,12 @@
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>197</v>
@@ -4423,7 +4429,7 @@
         <v>9</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>198</v>
@@ -4432,12 +4438,12 @@
         <v>10</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>199</v>
@@ -4446,7 +4452,7 @@
         <v>9</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>200</v>
@@ -4455,44 +4461,44 @@
         <v>10</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="C164" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E164" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C164" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E164" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="F164" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>21</v>
+        <v>180</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>206</v>
@@ -4506,7 +4512,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>207</v>
@@ -4515,7 +4521,7 @@
         <v>9</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>208</v>
@@ -4524,6 +4530,29 @@
         <v>10</v>
       </c>
       <c r="G166" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G167" s="2" t="s">
         <v>21</v>
       </c>
     </row>
